--- a/artfynd/A 34501-2022 artfynd.xlsx
+++ b/artfynd/A 34501-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150416</v>
+        <v>121150415</v>
       </c>
       <c r="B2" t="n">
-        <v>78598</v>
+        <v>78337</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482020</v>
+        <v>481919</v>
       </c>
       <c r="R2" t="n">
-        <v>6853653</v>
+        <v>6853650</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150415</v>
+        <v>121150417</v>
       </c>
       <c r="B3" t="n">
-        <v>78334</v>
+        <v>98081</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,30 +798,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481919</v>
+        <v>482027</v>
       </c>
       <c r="R3" t="n">
-        <v>6853650</v>
+        <v>6853647</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150417</v>
+        <v>121150416</v>
       </c>
       <c r="B4" t="n">
-        <v>98071</v>
+        <v>78601</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,30 +909,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482027</v>
+        <v>482020</v>
       </c>
       <c r="R4" t="n">
-        <v>6853647</v>
+        <v>6853653</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 34501-2022 artfynd.xlsx
+++ b/artfynd/A 34501-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150415</v>
+        <v>121150417</v>
       </c>
       <c r="B2" t="n">
-        <v>78337</v>
+        <v>98081</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481919</v>
+        <v>482027</v>
       </c>
       <c r="R2" t="n">
-        <v>6853650</v>
+        <v>6853647</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150417</v>
+        <v>121150415</v>
       </c>
       <c r="B3" t="n">
-        <v>98081</v>
+        <v>78337</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,30 +798,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482027</v>
+        <v>481919</v>
       </c>
       <c r="R3" t="n">
-        <v>6853647</v>
+        <v>6853650</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -1006,6 +1006,516 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121417437</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91973</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Svegardammen, Svegardammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>482034</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6853593</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121417502</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91973</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Svegardammen, Svegardammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>481952</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6853594</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121419373</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98081</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Svegardammen, Svegardammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>481995</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6853657</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121419297</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78601</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Svegardammen, Svegardammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>481958</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6853670</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121417584</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98081</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Svegardammen, Svegardammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>481916</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6853628</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34501-2022 artfynd.xlsx
+++ b/artfynd/A 34501-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150417</v>
+        <v>121150415</v>
       </c>
       <c r="B2" t="n">
-        <v>98081</v>
+        <v>78337</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482027</v>
+        <v>481919</v>
       </c>
       <c r="R2" t="n">
-        <v>6853647</v>
+        <v>6853650</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150415</v>
+        <v>121150417</v>
       </c>
       <c r="B3" t="n">
-        <v>78337</v>
+        <v>98081</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,30 +798,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481919</v>
+        <v>482027</v>
       </c>
       <c r="R3" t="n">
-        <v>6853650</v>
+        <v>6853647</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 34501-2022 artfynd.xlsx
+++ b/artfynd/A 34501-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150415</v>
+        <v>121150417</v>
       </c>
       <c r="B2" t="n">
-        <v>78337</v>
+        <v>98081</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481919</v>
+        <v>482027</v>
       </c>
       <c r="R2" t="n">
-        <v>6853650</v>
+        <v>6853647</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150417</v>
+        <v>121150416</v>
       </c>
       <c r="B3" t="n">
-        <v>98081</v>
+        <v>78601</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,30 +798,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482027</v>
+        <v>482020</v>
       </c>
       <c r="R3" t="n">
-        <v>6853647</v>
+        <v>6853653</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150416</v>
+        <v>121150415</v>
       </c>
       <c r="B4" t="n">
-        <v>78601</v>
+        <v>78337</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482020</v>
+        <v>481919</v>
       </c>
       <c r="R4" t="n">
-        <v>6853653</v>
+        <v>6853650</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121417437</v>
+        <v>121417584</v>
       </c>
       <c r="B5" t="n">
-        <v>91973</v>
+        <v>98081</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>482034</v>
+        <v>481916</v>
       </c>
       <c r="R5" t="n">
-        <v>6853593</v>
+        <v>6853628</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1098,19 +1098,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121417502</v>
+        <v>121417437</v>
       </c>
       <c r="B6" t="n">
         <v>91973</v>
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481952</v>
+        <v>482034</v>
       </c>
       <c r="R6" t="n">
-        <v>6853594</v>
+        <v>6853593</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1212,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121419373</v>
+        <v>121417502</v>
       </c>
       <c r="B7" t="n">
-        <v>98081</v>
+        <v>91973</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,25 +1224,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1252,13 +1252,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481995</v>
+        <v>481952</v>
       </c>
       <c r="R7" t="n">
-        <v>6853657</v>
+        <v>6853594</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121417584</v>
+        <v>121419373</v>
       </c>
       <c r="B9" t="n">
         <v>98081</v>
@@ -1456,13 +1456,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481916</v>
+        <v>481995</v>
       </c>
       <c r="R9" t="n">
-        <v>6853628</v>
+        <v>6853657</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1506,12 +1506,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 34501-2022 artfynd.xlsx
+++ b/artfynd/A 34501-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121150417</v>
       </c>
       <c r="B2" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>121150416</v>
       </c>
       <c r="B3" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>121150415</v>
       </c>
       <c r="B4" t="n">
-        <v>78337</v>
+        <v>78340</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121417584</v>
+        <v>121419373</v>
       </c>
       <c r="B5" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,13 +1048,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481916</v>
+        <v>481995</v>
       </c>
       <c r="R5" t="n">
-        <v>6853628</v>
+        <v>6853657</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,12 +1098,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1113,7 +1113,7 @@
         <v>121417437</v>
       </c>
       <c r="B6" t="n">
-        <v>91973</v>
+        <v>91985</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>121417502</v>
       </c>
       <c r="B7" t="n">
-        <v>91973</v>
+        <v>91985</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>121419297</v>
       </c>
       <c r="B8" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1416,10 +1416,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121419373</v>
+        <v>121417584</v>
       </c>
       <c r="B9" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1456,13 +1456,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481995</v>
+        <v>481916</v>
       </c>
       <c r="R9" t="n">
-        <v>6853657</v>
+        <v>6853628</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1506,12 +1506,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 34501-2022 artfynd.xlsx
+++ b/artfynd/A 34501-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150417</v>
+        <v>121150415</v>
       </c>
       <c r="B2" t="n">
-        <v>98094</v>
+        <v>78340</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482027</v>
+        <v>481919</v>
       </c>
       <c r="R2" t="n">
-        <v>6853647</v>
+        <v>6853650</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150415</v>
+        <v>121150417</v>
       </c>
       <c r="B4" t="n">
-        <v>78340</v>
+        <v>98095</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,30 +909,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481919</v>
+        <v>482027</v>
       </c>
       <c r="R4" t="n">
-        <v>6853650</v>
+        <v>6853647</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121419373</v>
+        <v>121417502</v>
       </c>
       <c r="B5" t="n">
-        <v>98094</v>
+        <v>91986</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,13 +1048,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481995</v>
+        <v>481952</v>
       </c>
       <c r="R5" t="n">
-        <v>6853657</v>
+        <v>6853594</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121417437</v>
+        <v>121419297</v>
       </c>
       <c r="B6" t="n">
-        <v>91985</v>
+        <v>78604</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,25 +1122,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482034</v>
+        <v>481958</v>
       </c>
       <c r="R6" t="n">
-        <v>6853593</v>
+        <v>6853670</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1200,22 +1200,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121417502</v>
+        <v>121419373</v>
       </c>
       <c r="B7" t="n">
-        <v>91985</v>
+        <v>98095</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,25 +1224,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1252,13 +1252,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481952</v>
+        <v>481995</v>
       </c>
       <c r="R7" t="n">
-        <v>6853594</v>
+        <v>6853657</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,10 +1314,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121419297</v>
+        <v>121417437</v>
       </c>
       <c r="B8" t="n">
-        <v>78604</v>
+        <v>91986</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1326,25 +1326,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481958</v>
+        <v>482034</v>
       </c>
       <c r="R8" t="n">
-        <v>6853670</v>
+        <v>6853593</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1404,12 +1404,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1419,7 +1419,7 @@
         <v>121417584</v>
       </c>
       <c r="B9" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 34501-2022 artfynd.xlsx
+++ b/artfynd/A 34501-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150415</v>
+        <v>121150416</v>
       </c>
       <c r="B2" t="n">
-        <v>78340</v>
+        <v>78607</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481919</v>
+        <v>482020</v>
       </c>
       <c r="R2" t="n">
-        <v>6853650</v>
+        <v>6853653</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150416</v>
+        <v>121150415</v>
       </c>
       <c r="B3" t="n">
-        <v>78604</v>
+        <v>78343</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482020</v>
+        <v>481919</v>
       </c>
       <c r="R3" t="n">
-        <v>6853653</v>
+        <v>6853650</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -900,7 +900,7 @@
         <v>121150417</v>
       </c>
       <c r="B4" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121417502</v>
+        <v>121419373</v>
       </c>
       <c r="B5" t="n">
-        <v>91986</v>
+        <v>98098</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,13 +1048,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481952</v>
+        <v>481995</v>
       </c>
       <c r="R5" t="n">
-        <v>6853594</v>
+        <v>6853657</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121419297</v>
+        <v>121417584</v>
       </c>
       <c r="B6" t="n">
-        <v>78604</v>
+        <v>98098</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,25 +1122,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481958</v>
+        <v>481916</v>
       </c>
       <c r="R6" t="n">
-        <v>6853670</v>
+        <v>6853628</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1212,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121419373</v>
+        <v>121417437</v>
       </c>
       <c r="B7" t="n">
-        <v>98095</v>
+        <v>91989</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,25 +1224,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1252,13 +1252,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481995</v>
+        <v>482034</v>
       </c>
       <c r="R7" t="n">
-        <v>6853657</v>
+        <v>6853593</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,10 +1314,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121417437</v>
+        <v>121417502</v>
       </c>
       <c r="B8" t="n">
-        <v>91986</v>
+        <v>91989</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482034</v>
+        <v>481952</v>
       </c>
       <c r="R8" t="n">
-        <v>6853593</v>
+        <v>6853594</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1416,10 +1416,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121417584</v>
+        <v>121419297</v>
       </c>
       <c r="B9" t="n">
-        <v>98095</v>
+        <v>78607</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1428,25 +1428,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481916</v>
+        <v>481958</v>
       </c>
       <c r="R9" t="n">
-        <v>6853628</v>
+        <v>6853670</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 34501-2022 artfynd.xlsx
+++ b/artfynd/A 34501-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150416</v>
+        <v>121150417</v>
       </c>
       <c r="B2" t="n">
-        <v>78607</v>
+        <v>98098</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482020</v>
+        <v>482027</v>
       </c>
       <c r="R2" t="n">
-        <v>6853653</v>
+        <v>6853647</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150415</v>
+        <v>121150416</v>
       </c>
       <c r="B3" t="n">
-        <v>78343</v>
+        <v>78607</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481919</v>
+        <v>482020</v>
       </c>
       <c r="R3" t="n">
-        <v>6853650</v>
+        <v>6853653</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150417</v>
+        <v>121150415</v>
       </c>
       <c r="B4" t="n">
-        <v>98098</v>
+        <v>78343</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,30 +909,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482027</v>
+        <v>481919</v>
       </c>
       <c r="R4" t="n">
-        <v>6853647</v>
+        <v>6853650</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121419373</v>
+        <v>121417584</v>
       </c>
       <c r="B5" t="n">
         <v>98098</v>
@@ -1048,13 +1048,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481995</v>
+        <v>481916</v>
       </c>
       <c r="R5" t="n">
-        <v>6853657</v>
+        <v>6853628</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,19 +1098,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121417584</v>
+        <v>121419373</v>
       </c>
       <c r="B6" t="n">
         <v>98098</v>
@@ -1150,13 +1150,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481916</v>
+        <v>481995</v>
       </c>
       <c r="R6" t="n">
-        <v>6853628</v>
+        <v>6853657</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1200,19 +1200,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121417437</v>
+        <v>121417502</v>
       </c>
       <c r="B7" t="n">
         <v>91989</v>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482034</v>
+        <v>481952</v>
       </c>
       <c r="R7" t="n">
-        <v>6853593</v>
+        <v>6853594</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1314,7 +1314,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121417502</v>
+        <v>121417437</v>
       </c>
       <c r="B8" t="n">
         <v>91989</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481952</v>
+        <v>482034</v>
       </c>
       <c r="R8" t="n">
-        <v>6853594</v>
+        <v>6853593</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>

--- a/artfynd/A 34501-2022 artfynd.xlsx
+++ b/artfynd/A 34501-2022 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121417584</v>
+        <v>121417502</v>
       </c>
       <c r="B5" t="n">
-        <v>98098</v>
+        <v>91995</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481916</v>
+        <v>481952</v>
       </c>
       <c r="R5" t="n">
-        <v>6853628</v>
+        <v>6853594</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1098,22 +1098,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121419373</v>
+        <v>121417437</v>
       </c>
       <c r="B6" t="n">
-        <v>98098</v>
+        <v>91995</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,25 +1122,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1150,13 +1150,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481995</v>
+        <v>482034</v>
       </c>
       <c r="R6" t="n">
-        <v>6853657</v>
+        <v>6853593</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121417502</v>
+        <v>121419373</v>
       </c>
       <c r="B7" t="n">
-        <v>91989</v>
+        <v>98104</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,25 +1224,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1252,13 +1252,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481952</v>
+        <v>481995</v>
       </c>
       <c r="R7" t="n">
-        <v>6853594</v>
+        <v>6853657</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,10 +1314,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121417437</v>
+        <v>121419297</v>
       </c>
       <c r="B8" t="n">
-        <v>91989</v>
+        <v>78608</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1326,25 +1326,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482034</v>
+        <v>481958</v>
       </c>
       <c r="R8" t="n">
-        <v>6853593</v>
+        <v>6853670</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1404,22 +1404,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121419297</v>
+        <v>121417584</v>
       </c>
       <c r="B9" t="n">
-        <v>78607</v>
+        <v>98104</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1428,25 +1428,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481958</v>
+        <v>481916</v>
       </c>
       <c r="R9" t="n">
-        <v>6853670</v>
+        <v>6853628</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 34501-2022 artfynd.xlsx
+++ b/artfynd/A 34501-2022 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121417502</v>
+        <v>121417437</v>
       </c>
       <c r="B5" t="n">
-        <v>91995</v>
+        <v>91996</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481952</v>
+        <v>482034</v>
       </c>
       <c r="R5" t="n">
-        <v>6853594</v>
+        <v>6853593</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1110,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121417437</v>
+        <v>121419373</v>
       </c>
       <c r="B6" t="n">
-        <v>91995</v>
+        <v>98105</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,25 +1122,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1150,13 +1150,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482034</v>
+        <v>481995</v>
       </c>
       <c r="R6" t="n">
-        <v>6853593</v>
+        <v>6853657</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121419373</v>
+        <v>121417584</v>
       </c>
       <c r="B7" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,13 +1252,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481995</v>
+        <v>481916</v>
       </c>
       <c r="R7" t="n">
-        <v>6853657</v>
+        <v>6853628</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1302,12 +1302,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1317,7 +1317,7 @@
         <v>121419297</v>
       </c>
       <c r="B8" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1416,10 +1416,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121417584</v>
+        <v>121417502</v>
       </c>
       <c r="B9" t="n">
-        <v>98104</v>
+        <v>91996</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1428,25 +1428,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481916</v>
+        <v>481952</v>
       </c>
       <c r="R9" t="n">
-        <v>6853628</v>
+        <v>6853594</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1506,12 +1506,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 34501-2022 artfynd.xlsx
+++ b/artfynd/A 34501-2022 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121417437</v>
+        <v>121419297</v>
       </c>
       <c r="B5" t="n">
-        <v>91996</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>482034</v>
+        <v>481958</v>
       </c>
       <c r="R5" t="n">
-        <v>6853593</v>
+        <v>6853670</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1098,22 +1098,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121419373</v>
+        <v>121417502</v>
       </c>
       <c r="B6" t="n">
-        <v>98105</v>
+        <v>91996</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,25 +1122,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1150,13 +1150,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481995</v>
+        <v>481952</v>
       </c>
       <c r="R6" t="n">
-        <v>6853657</v>
+        <v>6853594</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1314,10 +1314,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121419297</v>
+        <v>121419373</v>
       </c>
       <c r="B8" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1326,25 +1326,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,13 +1354,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481958</v>
+        <v>481995</v>
       </c>
       <c r="R8" t="n">
-        <v>6853670</v>
+        <v>6853657</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1404,19 +1404,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121417502</v>
+        <v>121417437</v>
       </c>
       <c r="B9" t="n">
         <v>91996</v>
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481952</v>
+        <v>482034</v>
       </c>
       <c r="R9" t="n">
-        <v>6853594</v>
+        <v>6853593</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 34501-2022 artfynd.xlsx
+++ b/artfynd/A 34501-2022 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121419297</v>
+        <v>121419373</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,13 +1048,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481958</v>
+        <v>481995</v>
       </c>
       <c r="R5" t="n">
-        <v>6853670</v>
+        <v>6853657</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,12 +1098,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1212,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121417584</v>
+        <v>121417437</v>
       </c>
       <c r="B7" t="n">
-        <v>98105</v>
+        <v>91996</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,25 +1224,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481916</v>
+        <v>482034</v>
       </c>
       <c r="R7" t="n">
-        <v>6853628</v>
+        <v>6853593</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1302,22 +1302,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121419373</v>
+        <v>121419297</v>
       </c>
       <c r="B8" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1326,25 +1326,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,13 +1354,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481995</v>
+        <v>481958</v>
       </c>
       <c r="R8" t="n">
-        <v>6853657</v>
+        <v>6853670</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1404,22 +1404,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121417437</v>
+        <v>121417584</v>
       </c>
       <c r="B9" t="n">
-        <v>91996</v>
+        <v>98105</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1428,25 +1428,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>482034</v>
+        <v>481916</v>
       </c>
       <c r="R9" t="n">
-        <v>6853593</v>
+        <v>6853628</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1506,12 +1506,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 34501-2022 artfynd.xlsx
+++ b/artfynd/A 34501-2022 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121419373</v>
+        <v>121417502</v>
       </c>
       <c r="B5" t="n">
-        <v>98105</v>
+        <v>91996</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,13 +1048,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481995</v>
+        <v>481952</v>
       </c>
       <c r="R5" t="n">
-        <v>6853657</v>
+        <v>6853594</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121417502</v>
+        <v>121419297</v>
       </c>
       <c r="B6" t="n">
-        <v>91996</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,25 +1122,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481952</v>
+        <v>481958</v>
       </c>
       <c r="R6" t="n">
-        <v>6853594</v>
+        <v>6853670</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1200,22 +1200,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121417437</v>
+        <v>121419373</v>
       </c>
       <c r="B7" t="n">
-        <v>91996</v>
+        <v>98105</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,25 +1224,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1252,13 +1252,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482034</v>
+        <v>481995</v>
       </c>
       <c r="R7" t="n">
-        <v>6853593</v>
+        <v>6853657</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,10 +1314,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121419297</v>
+        <v>121417437</v>
       </c>
       <c r="B8" t="n">
-        <v>78609</v>
+        <v>91996</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1326,25 +1326,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481958</v>
+        <v>482034</v>
       </c>
       <c r="R8" t="n">
-        <v>6853670</v>
+        <v>6853593</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1404,12 +1404,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 34501-2022 artfynd.xlsx
+++ b/artfynd/A 34501-2022 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121417502</v>
+        <v>121419297</v>
       </c>
       <c r="B5" t="n">
-        <v>91996</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481952</v>
+        <v>481958</v>
       </c>
       <c r="R5" t="n">
-        <v>6853594</v>
+        <v>6853670</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1098,22 +1098,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121419297</v>
+        <v>121419373</v>
       </c>
       <c r="B6" t="n">
-        <v>78609</v>
+        <v>98113</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,25 +1122,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1150,13 +1150,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481958</v>
+        <v>481995</v>
       </c>
       <c r="R6" t="n">
-        <v>6853670</v>
+        <v>6853657</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1200,22 +1200,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121419373</v>
+        <v>121417437</v>
       </c>
       <c r="B7" t="n">
-        <v>98105</v>
+        <v>92004</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,25 +1224,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1252,13 +1252,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481995</v>
+        <v>482034</v>
       </c>
       <c r="R7" t="n">
-        <v>6853657</v>
+        <v>6853593</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,10 +1314,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121417437</v>
+        <v>121417502</v>
       </c>
       <c r="B8" t="n">
-        <v>91996</v>
+        <v>92004</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482034</v>
+        <v>481952</v>
       </c>
       <c r="R8" t="n">
-        <v>6853593</v>
+        <v>6853594</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1419,7 +1419,7 @@
         <v>121417584</v>
       </c>
       <c r="B9" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 34501-2022 artfynd.xlsx
+++ b/artfynd/A 34501-2022 artfynd.xlsx
@@ -1110,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121419373</v>
+        <v>121417437</v>
       </c>
       <c r="B6" t="n">
-        <v>98113</v>
+        <v>92004</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,25 +1122,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1150,13 +1150,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481995</v>
+        <v>482034</v>
       </c>
       <c r="R6" t="n">
-        <v>6853657</v>
+        <v>6853593</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121417437</v>
+        <v>121419373</v>
       </c>
       <c r="B7" t="n">
-        <v>92004</v>
+        <v>98113</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,25 +1224,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1252,13 +1252,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482034</v>
+        <v>481995</v>
       </c>
       <c r="R7" t="n">
-        <v>6853593</v>
+        <v>6853657</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 34501-2022 artfynd.xlsx
+++ b/artfynd/A 34501-2022 artfynd.xlsx
@@ -1110,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121417437</v>
+        <v>121419373</v>
       </c>
       <c r="B6" t="n">
-        <v>92004</v>
+        <v>98113</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,25 +1122,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1150,13 +1150,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482034</v>
+        <v>481995</v>
       </c>
       <c r="R6" t="n">
-        <v>6853593</v>
+        <v>6853657</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121419373</v>
+        <v>121417437</v>
       </c>
       <c r="B7" t="n">
-        <v>98113</v>
+        <v>92004</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,25 +1224,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1252,13 +1252,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481995</v>
+        <v>482034</v>
       </c>
       <c r="R7" t="n">
-        <v>6853657</v>
+        <v>6853593</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
